--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T03:12:48+00:00</t>
+    <t>2026-03-18T09:54:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T09:54:13+00:00</t>
+    <t>2026-03-23T13:24:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:24:52+00:00</t>
+    <t>2026-03-25T02:48:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T02:48:03+00:00</t>
+    <t>2026-03-25T03:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:05:28+00:00</t>
+    <t>2026-03-25T03:10:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:10:05+00:00</t>
+    <t>2026-03-25T03:15:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:15:34+00:00</t>
+    <t>2026-03-25T03:26:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:26:10+00:00</t>
+    <t>2026-03-25T03:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:31:02+00:00</t>
+    <t>2026-03-25T03:34:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:34:45+00:00</t>
+    <t>2026-03-25T03:48:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:48:45+00:00</t>
+    <t>2026-03-25T03:54:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T03:54:03+00:00</t>
+    <t>2026-04-01T03:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:21:07+00:00</t>
+    <t>2026-04-01T03:34:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Philippines</t>
+    <t>Philippines (the)</t>
   </si>
   <si>
     <t>Description</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:34:09+00:00</t>
+    <t>2026-04-01T03:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T03:44:59+00:00</t>
+    <t>2026-04-06T07:53:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-06T07:53:57+00:00</t>
+    <t>2026-04-08T04:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-educational-attainment.xlsx
+++ b/dev/StructureDefinition-educational-attainment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:01:15+00:00</t>
+    <t>2026-04-13T08:21:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
